--- a/education_forms/050_spelling_quiz--education_forms.xlsx
+++ b/education_forms/050_spelling_quiz--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -707,7 +707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C138"/>
+  <dimension ref="A1:C76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>be</t>
+          <t>we</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>be</t>
+          <t>we</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>we</t>
+          <t>an</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>we</t>
+          <t>an</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>an</t>
+          <t>you</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>an</t>
+          <t>you</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>you</t>
+          <t>all</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>you</t>
+          <t>all</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>would</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>would</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>would</t>
+          <t>up</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>would</t>
+          <t>up</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>up</t>
+          <t>out</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>up</t>
+          <t>out</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>out</t>
+          <t>us</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>out</t>
+          <t>us</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>us</t>
+          <t>my</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>us</t>
+          <t>my</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>my</t>
+          <t>your</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>my</t>
+          <t>your</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>your</t>
+          <t>her</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>your</t>
+          <t>her</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>her</t>
+          <t>he</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>her</t>
+          <t>he</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>he</t>
+          <t>it</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>he</t>
+          <t>it</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>it</t>
+          <t>not</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>it</t>
+          <t>not</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>not</t>
+          <t>what</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>not</t>
+          <t>what</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>what</t>
+          <t>when</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>what</t>
+          <t>when</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>when</t>
+          <t>then</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>when</t>
+          <t>then</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>then</t>
+          <t>here</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>then</t>
+          <t>here</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>here</t>
+          <t>there</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>here</t>
+          <t>there</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>there</t>
+          <t>than</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>there</t>
+          <t>than</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>than</t>
+          <t>has</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>than</t>
+          <t>has</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>have</t>
+          <t>every</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>have</t>
+          <t>every</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>has</t>
+          <t>who</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>has</t>
+          <t>who</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>every</t>
+          <t>by</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>every</t>
+          <t>by</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>who</t>
+          <t>or</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>who</t>
+          <t>or</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>what</t>
+          <t>so</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>what</t>
+          <t>so</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>that</t>
+          <t>but</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>that</t>
+          <t>but</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>for</t>
+          <t>like</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>for</t>
+          <t>like</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>with</t>
+          <t>now</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>with</t>
+          <t>now</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>as</t>
+          <t>being</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>as</t>
+          <t>being</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>on</t>
+          <t>only</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>on</t>
+          <t>only</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>at</t>
+          <t>own</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>at</t>
+          <t>own</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>by</t>
+          <t>see</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>by</t>
+          <t>see</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>to</t>
+          <t>under</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>to</t>
+          <t>under</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>from</t>
+          <t>can</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>from</t>
+          <t>can</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>and</t>
+          <t>year</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>and</t>
+          <t>year</t>
         </is>
       </c>
     </row>
@@ -1828,12 +1828,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>in</t>
+          <t>might</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>in</t>
+          <t>might</t>
         </is>
       </c>
     </row>
@@ -1845,12 +1845,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>is</t>
+          <t>few</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>is</t>
+          <t>few</t>
         </is>
       </c>
     </row>
@@ -1862,12 +1862,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>or</t>
+          <t>also</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>or</t>
+          <t>also</t>
         </is>
       </c>
     </row>
@@ -1879,12 +1879,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>of</t>
+          <t>ask</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>of</t>
+          <t>ask</t>
         </is>
       </c>
     </row>
@@ -1896,12 +1896,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>so</t>
+          <t>about</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>so</t>
+          <t>about</t>
         </is>
       </c>
     </row>
@@ -1913,12 +1913,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>than</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>than</t>
+          <t>often</t>
         </is>
       </c>
     </row>
@@ -1930,12 +1930,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>but</t>
+          <t>use</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>but</t>
+          <t>use</t>
         </is>
       </c>
     </row>
@@ -1947,12 +1947,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>have</t>
+          <t>such</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>have</t>
+          <t>such</t>
         </is>
       </c>
     </row>
@@ -1964,12 +1964,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>like</t>
+          <t>could</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>like</t>
+          <t>could</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>when</t>
+          <t>been</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>when</t>
+          <t>been</t>
         </is>
       </c>
     </row>
@@ -1998,1064 +1998,10 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>then</t>
+          <t>where</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
-        <is>
-          <t>then</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>word_choices</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>there</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>there</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>word_choices</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>now</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>now</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>word_choices</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>being</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>being</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>word_choices</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>only</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>only</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>word_choices</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>own</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>own</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>word_choices</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>see</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>see</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>word_choices</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>word_choices</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>can</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>can</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>word_choices</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>year</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>year</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>word_choices</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>might</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>might</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>word_choices</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>few</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>few</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>word_choices</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>also</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>also</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>word_choices</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>word_choices</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>about</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>about</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>word_choices</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>often</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>often</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>word_choices</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>being</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>being</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>word_choices</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>use</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>use</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>word_choices</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>such</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>such</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>word_choices</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>have</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>have</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>word_choices</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>could</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>could</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>word_choices</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>what</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>what</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>word_choices</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>been</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>been</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>word_choices</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>been</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>been</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>word_choices</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>like</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>like</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>word_choices</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>being</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>being</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>word_choices</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>there</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>there</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>word_choices</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>here</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>here</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>word_choices</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>been</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>been</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>word_choices</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>there</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>there</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>word_choices</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>where</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>where</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>word_choices</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>being</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>being</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>word_choices</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>been</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>been</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>word_choices</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>where</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>where</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>word_choices</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>being</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>being</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>word_choices</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>here</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>here</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>word_choices</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>there</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>there</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>word_choices</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>being</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>being</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>word_choices</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>where</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>where</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>word_choices</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>been</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>been</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>word_choices</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>there</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>there</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>word_choices</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>being</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>being</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>word_choices</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>where</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>where</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>word_choices</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>here</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>here</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>word_choices</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>there</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>there</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>word_choices</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>being</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>being</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>word_choices</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>where</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>where</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>word_choices</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>been</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>been</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>word_choices</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>there</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>there</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>word_choices</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>being</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>being</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>word_choices</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>where</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>where</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>word_choices</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>here</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>here</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>word_choices</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>there</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>there</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>word_choices</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>being</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>being</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>word_choices</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>where</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>where</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>word_choices</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>been</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>been</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>word_choices</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>there</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>there</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>word_choices</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>being</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>being</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>word_choices</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>where</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>where</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>word_choices</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>here</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>here</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>word_choices</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>there</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>there</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>word_choices</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>being</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>being</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>word_choices</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>where</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
         <is>
           <t>where</t>
         </is>
